--- a/res/drive/text assets/pstory_003/adv_pstory_003_kllj_final-normal-02.xlsx
+++ b/res/drive/text assets/pstory_003/adv_pstory_003_kllj_final-normal-02.xlsx
@@ -1,40 +1,114 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>translated name</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>translated text</t>
+  </si>
+  <si>
+    <t>リーリヤ</t>
+  </si>
+  <si>
+    <t>{user}</t>
+  </si>
+  <si>
+    <t>리리야</t>
+  </si>
+  <si>
+    <t>センパイ！
+ついに、本番ですね……！</t>
+  </si>
+  <si>
+    <t>相手はすごいアイドルばかりだけど……</t>
+  </si>
+  <si>
+    <t>わたしたちも、少しずつ
+積み重ねてきました。</t>
+  </si>
+  <si>
+    <t>信じましょう。
+俺たちが歩んできた道を。</t>
+  </si>
+  <si>
+    <t>はい！　葛城リーリヤ、
+『REVERSI』、行きます！</t>
+  </si>
+  <si>
+    <t>선배!
+드디어, 본무대네요……!</t>
+  </si>
+  <si>
+    <t>상대는 대단한 아이돌들뿐이지만……</t>
+  </si>
+  <si>
+    <t>저희도, 조금씩
+쌓아올려 왔어요.</t>
+  </si>
+  <si>
+    <t>믿읍시다.
+저희가 걸어온 길을.</t>
+  </si>
+  <si>
+    <t>네! 카츠라기 릴리야,
+『REVERSI』, 갑니다!</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -65,89 +139,25 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -435,176 +445,114 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="15.7109375" customWidth="1" style="1" min="1" max="3"/>
-    <col width="70.7109375" customWidth="1" style="2" min="4" max="5"/>
+    <col min="1" max="3" width="15.7109375" style="1" customWidth="1"/>
+    <col min="4" max="5" width="70.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>translated name</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>translated text</t>
-        </is>
+    <row r="1" spans="1:5">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
+    <row r="2" spans="1:5">
+      <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>リーリヤ</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>리리야</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>センパイ！
-ついに、本番ですね……！</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>선배!
-드디어, 본무대네요……!</t>
-        </is>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
+    <row r="3" spans="1:5">
+      <c r="A3" s="1">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>リーリヤ</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>리리야</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>相手はすごいアイドルばかりだけど……</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>상대는 대단한 아이돌들뿐이지만……</t>
-        </is>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
+    <row r="4" spans="1:5">
+      <c r="A4" s="1">
         <v>0</v>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>リーリヤ</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>리리야</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>わたしたちも、少しずつ
-積み重ねてきました。</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>우리도, 조금씩
-쌓아 왔어요.</t>
-        </is>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
+    <row r="5" spans="1:5">
+      <c r="A5" s="1">
         <v>0</v>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>{user}</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>{user}</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>信じましょう。
-俺たちが歩んできた道を。</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>믿읍시다.
-우리가 걸어온 길을.</t>
-        </is>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
+    <row r="6" spans="1:5">
+      <c r="A6" s="1">
         <v>0</v>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>リーリヤ</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>리리야</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>はい！　葛城リーリヤ、
-『REVERSI』、行きます！</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>네! 가쓰라기 리리야,
-『REVERSI』, 갑니다!</t>
-        </is>
+      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
